--- a/Invoices To Do.xlsx
+++ b/Invoices To Do.xlsx
@@ -391,7 +391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.28515625" customWidth="1" style="1" min="1" max="1"/>

--- a/Invoices To Do.xlsx
+++ b/Invoices To Do.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -391,11 +391,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="37.28515625" customWidth="1" style="1" min="1" max="1"/>
-    <col width="12.42578125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="37.33203125" customWidth="1" style="1" min="1" max="1"/>
+    <col width="12.44140625" bestFit="1" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -412,6 +412,7 @@
     </row>
     <row r="2"/>
     <row r="3" ht="15.75" customHeight="1"/>
+    <row r="4"/>
     <row r="15" ht="15.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Invoices To Do.xlsx
+++ b/Invoices To Do.xlsx
@@ -391,7 +391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="37.33203125" customWidth="1" style="1" min="1" max="1"/>
@@ -412,7 +412,6 @@
     </row>
     <row r="2"/>
     <row r="3" ht="15.75" customHeight="1"/>
-    <row r="4"/>
     <row r="15" ht="15.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Invoices To Do.xlsx
+++ b/Invoices To Do.xlsx
@@ -391,7 +391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="37.33203125" customWidth="1" style="1" min="1" max="1"/>
@@ -410,8 +410,55 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3" ht="15.75" customHeight="1"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2446665619</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Toronto Hydro</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>5507910887</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Toronto Hydro</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>9621400000</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Toronto Hydro</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>7097902373</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Toronto Hydro</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="15" ht="15.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Invoices To Do.xlsx
+++ b/Invoices To Do.xlsx
@@ -391,7 +391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="37.33203125" customWidth="1" style="1" min="1" max="1"/>
@@ -410,55 +410,19 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2446665619</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Toronto Hydro</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>5507910887</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Toronto Hydro</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>9621400000</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Toronto Hydro</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>7097902373</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Toronto Hydro</t>
-        </is>
-      </c>
-    </row>
+    <row r="2"/>
+    <row r="3" ht="15.75" customHeight="1"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15" ht="15.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
